--- a/data/trans_dic/Q17F_D_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 26,46</t>
+          <t>8,52; 27,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 19,66</t>
+          <t>5,14; 20,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 20,69</t>
+          <t>5,01; 19,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,43; 33,59</t>
+          <t>17,28; 34,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 24,71</t>
+          <t>6,04; 22,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 18,2</t>
+          <t>3,86; 17,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 23,07</t>
+          <t>6,77; 21,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 25,84</t>
+          <t>13,52; 25,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 22,88</t>
+          <t>10,12; 21,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,94</t>
+          <t>5,83; 15,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 17,57</t>
+          <t>7,18; 17,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 28,17</t>
+          <t>17,3; 27,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 24,7</t>
+          <t>6,06; 24,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,26</t>
+          <t>3,15; 15,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 19,43</t>
+          <t>5,03; 18,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 28,21</t>
+          <t>11,69; 27,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 20,84</t>
+          <t>6,55; 21,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 17,31</t>
+          <t>4,25; 16,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 29,12</t>
+          <t>12,3; 29,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,03; 24,29</t>
+          <t>11,79; 25,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 19,17</t>
+          <t>8,01; 19,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 13,24</t>
+          <t>5,29; 13,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 21,86</t>
+          <t>10,3; 21,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 23,71</t>
+          <t>13,42; 23,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 19,47</t>
+          <t>7,37; 19,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 25,56</t>
+          <t>12,47; 25,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,81</t>
+          <t>2,64; 10,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 22,57</t>
+          <t>8,72; 21,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 25,92</t>
+          <t>5,29; 25,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,83</t>
+          <t>4,76; 17,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 19,24</t>
+          <t>4,81; 20,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 34,07</t>
+          <t>14,14; 34,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 18,15</t>
+          <t>8,04; 18,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,59</t>
+          <t>10,62; 20,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,24</t>
+          <t>4,07; 11,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 24,09</t>
+          <t>12,71; 24,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,16</t>
+          <t>8,13; 15,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,88; 17,75</t>
+          <t>8,62; 17,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 17,79</t>
+          <t>9,38; 17,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 21,92</t>
+          <t>11,47; 21,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 14,84</t>
+          <t>6,43; 15,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 18,12</t>
+          <t>9,15; 18,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 15,99</t>
+          <t>7,93; 16,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,44; 27,08</t>
+          <t>16,55; 27,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,24</t>
+          <t>8,22; 13,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 16,12</t>
+          <t>10,02; 15,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,53</t>
+          <t>9,65; 15,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,44</t>
+          <t>15,36; 22,6</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 20,45</t>
+          <t>5,53; 19,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 16,52</t>
+          <t>5,21; 18,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 18,49</t>
+          <t>7,63; 18,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 27,44</t>
+          <t>11,27; 27,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 17,03</t>
+          <t>7,7; 17,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,33</t>
+          <t>5,04; 11,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 18,17</t>
+          <t>9,12; 18,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 20,62</t>
+          <t>5,98; 20,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 16,46</t>
+          <t>8,29; 16,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,53</t>
+          <t>5,81; 11,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 16,47</t>
+          <t>9,89; 16,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 20,61</t>
+          <t>7,8; 20,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,91</t>
+          <t>0,0; 29,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 30,63</t>
+          <t>5,28; 31,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 18,45</t>
+          <t>2,51; 20,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,13</t>
+          <t>1,98; 40,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,5</t>
+          <t>6,31; 12,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,3</t>
+          <t>8,89; 16,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 15,02</t>
+          <t>8,14; 15,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,82; 26,49</t>
+          <t>14,62; 26,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,1</t>
+          <t>6,4; 12,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 16,24</t>
+          <t>9,2; 16,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,89</t>
+          <t>8,12; 14,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,05; 25,75</t>
+          <t>13,89; 25,46</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,86; 15,27</t>
+          <t>9,79; 15,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,2</t>
+          <t>10,3; 15,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,39</t>
+          <t>8,56; 13,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,17</t>
+          <t>15,25; 21,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,79</t>
+          <t>8,64; 12,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,47</t>
+          <t>8,69; 12,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,72</t>
+          <t>10,58; 14,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,4; 20,82</t>
+          <t>12,73; 20,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,93</t>
+          <t>9,87; 13,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,06</t>
+          <t>10,03; 13,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 13,37</t>
+          <t>10,35; 13,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,46; 20,16</t>
+          <t>15,06; 20,16</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7086; 20748</t>
+          <t>6680; 21243</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3916; 15113</t>
+          <t>3950; 15475</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5325; 19807</t>
+          <t>4791; 19042</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19829; 38212</t>
+          <t>19659; 39580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6168; 18534</t>
+          <t>4527; 17006</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3763; 13986</t>
+          <t>2962; 13464</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6323; 20996</t>
+          <t>6161; 19647</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13803; 26432</t>
+          <t>13836; 26333</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16065; 35098</t>
+          <t>15526; 33145</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9484; 24494</t>
+          <t>8960; 23378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13892; 32801</t>
+          <t>13410; 32995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37512; 60863</t>
+          <t>37378; 59843</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3660; 14497</t>
+          <t>3554; 14451</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3164; 13729</t>
+          <t>2830; 13649</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4772; 17837</t>
+          <t>4622; 17342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11005; 25000</t>
+          <t>10358; 24793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5877; 18480</t>
+          <t>5806; 19182</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4710; 16393</t>
+          <t>4029; 15808</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11198; 26409</t>
+          <t>11158; 26470</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10503; 21214</t>
+          <t>10293; 22108</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11358; 28248</t>
+          <t>11800; 28610</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9455; 24452</t>
+          <t>9771; 24897</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19937; 39905</t>
+          <t>18795; 39283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23716; 41721</t>
+          <t>23612; 41702</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8455; 22321</t>
+          <t>8444; 22009</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18187; 38874</t>
+          <t>18965; 38820</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4016; 16439</t>
+          <t>4009; 16141</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7095; 18824</t>
+          <t>7273; 18040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2734; 14215</t>
+          <t>2901; 13748</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4110; 14781</t>
+          <t>4180; 15717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2120; 11490</t>
+          <t>2871; 12515</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6870; 16073</t>
+          <t>6668; 16074</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13724; 30757</t>
+          <t>13624; 30704</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25590; 49398</t>
+          <t>25483; 49485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8571; 23794</t>
+          <t>8616; 25053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16192; 31457</t>
+          <t>16589; 32192</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20420; 39476</t>
+          <t>21178; 40313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25069; 50115</t>
+          <t>24332; 48346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25832; 49582</t>
+          <t>26147; 49932</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23019; 44462</t>
+          <t>23265; 44141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13640; 30753</t>
+          <t>13319; 31827</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21267; 42950</t>
+          <t>21686; 43730</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20109; 40958</t>
+          <t>20317; 41304</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29407; 48432</t>
+          <t>29589; 48493</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38072; 66577</t>
+          <t>38446; 64188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52613; 83692</t>
+          <t>52047; 82512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50972; 83088</t>
+          <t>51622; 83195</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57051; 85656</t>
+          <t>58625; 86275</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3866; 14165</t>
+          <t>3832; 13618</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5192; 17388</t>
+          <t>5483; 19038</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12549; 29067</t>
+          <t>11995; 28745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9987; 23256</t>
+          <t>9550; 23429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12216; 29781</t>
+          <t>13458; 31140</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12654; 30682</t>
+          <t>13646; 31319</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23181; 45655</t>
+          <t>22908; 45347</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15802; 52741</t>
+          <t>15284; 53019</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20042; 40171</t>
+          <t>20223; 39860</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22759; 43365</t>
+          <t>21835; 44039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39787; 67306</t>
+          <t>40412; 67511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26318; 70160</t>
+          <t>26542; 68559</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6650</t>
+          <t>0; 6060</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1018; 11197</t>
+          <t>1932; 11689</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1039; 7511</t>
+          <t>1022; 8439</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 8248</t>
+          <t>429; 8657</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22994; 45980</t>
+          <t>23207; 44228</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30842; 55372</t>
+          <t>30193; 54561</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28358; 53189</t>
+          <t>28831; 54069</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23961; 42833</t>
+          <t>23645; 43508</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23685; 47020</t>
+          <t>24860; 48568</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34503; 61103</t>
+          <t>34641; 60233</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32153; 58806</t>
+          <t>32050; 58322</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25758; 47210</t>
+          <t>25471; 46679</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>59373; 91973</t>
+          <t>58925; 91922</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74914; 112917</t>
+          <t>76505; 115353</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71659; 109319</t>
+          <t>69880; 108106</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90746; 125979</t>
+          <t>90730; 126341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>85481; 123824</t>
+          <t>83660; 124655</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96813; 138068</t>
+          <t>96242; 140267</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>116484; 162377</t>
+          <t>116671; 163042</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>111657; 173480</t>
+          <t>106045; 173090</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154589; 203129</t>
+          <t>154951; 204881</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185360; 241705</t>
+          <t>185595; 240514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201105; 256702</t>
+          <t>198714; 257442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>220798; 287957</t>
+          <t>215089; 287907</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q17F_D_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 27,1</t>
+          <t>9,16; 27,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 20,13</t>
+          <t>5,03; 18,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 19,89</t>
+          <t>5,34; 19,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 34,79</t>
+          <t>17,84; 33,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 22,68</t>
+          <t>7,17; 24,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 17,52</t>
+          <t>3,9; 17,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 21,59</t>
+          <t>6,63; 22,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 25,74</t>
+          <t>15,52; 28,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 21,61</t>
+          <t>10,17; 22,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 15,21</t>
+          <t>6,1; 16,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 17,67</t>
+          <t>7,2; 17,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 27,69</t>
+          <t>17,91; 28,62</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 24,63</t>
+          <t>5,81; 23,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 15,17</t>
+          <t>3,39; 14,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,89</t>
+          <t>5,2; 19,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 27,97</t>
+          <t>11,72; 26,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 21,64</t>
+          <t>6,49; 21,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 16,69</t>
+          <t>4,18; 16,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 29,18</t>
+          <t>12,58; 29,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,79; 25,32</t>
+          <t>11,35; 24,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 19,42</t>
+          <t>7,95; 18,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 13,48</t>
+          <t>5,34; 13,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,52</t>
+          <t>10,89; 21,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 23,7</t>
+          <t>12,92; 22,51</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 19,2</t>
+          <t>7,48; 19,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 25,52</t>
+          <t>12,12; 25,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,62</t>
+          <t>2,28; 11,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 21,63</t>
+          <t>9,7; 24,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 25,07</t>
+          <t>4,9; 23,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,9</t>
+          <t>4,55; 17,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 20,96</t>
+          <t>3,49; 20,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 34,08</t>
+          <t>14,56; 33,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,12</t>
+          <t>7,94; 18,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 20,63</t>
+          <t>9,89; 19,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,83</t>
+          <t>4,03; 11,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 24,66</t>
+          <t>13,01; 25,43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 15,48</t>
+          <t>7,81; 16,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 17,13</t>
+          <t>8,9; 17,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 17,91</t>
+          <t>9,59; 18,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 21,76</t>
+          <t>11,86; 22,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 15,36</t>
+          <t>6,49; 15,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 18,45</t>
+          <t>8,77; 17,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,12</t>
+          <t>7,62; 15,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 27,12</t>
+          <t>17,19; 27,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,73</t>
+          <t>8,33; 14,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,89</t>
+          <t>10,07; 16,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 15,55</t>
+          <t>9,31; 15,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 22,6</t>
+          <t>15,68; 23,03</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 19,66</t>
+          <t>6,24; 21,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 18,09</t>
+          <t>5,2; 17,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 18,28</t>
+          <t>8,1; 18,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 27,65</t>
+          <t>11,14; 26,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,81</t>
+          <t>7,12; 17,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,56</t>
+          <t>4,98; 11,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,12; 18,04</t>
+          <t>9,41; 18,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 20,73</t>
+          <t>15,41; 24,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 16,33</t>
+          <t>7,79; 16,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 11,71</t>
+          <t>5,86; 11,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 16,52</t>
+          <t>9,83; 16,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 20,14</t>
+          <t>15,57; 23,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,08</t>
+          <t>0,0; 29,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 31,98</t>
+          <t>2,76; 30,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 20,73</t>
+          <t>2,5; 20,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 40,02</t>
+          <t>2,1; 41,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,03</t>
+          <t>6,32; 12,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 16,06</t>
+          <t>8,62; 16,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 15,27</t>
+          <t>8,34; 15,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,62; 26,91</t>
+          <t>14,25; 25,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,5</t>
+          <t>6,5; 12,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 16,0</t>
+          <t>9,12; 16,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,12; 14,77</t>
+          <t>8,16; 14,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 25,46</t>
+          <t>13,91; 24,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,79; 15,27</t>
+          <t>9,58; 15,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,3; 15,52</t>
+          <t>10,22; 15,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,24</t>
+          <t>8,61; 13,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,23</t>
+          <t>15,59; 21,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,87</t>
+          <t>8,75; 12,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 12,67</t>
+          <t>8,86; 12,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,78</t>
+          <t>10,47; 14,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 20,78</t>
+          <t>18,02; 22,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,05</t>
+          <t>9,81; 12,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 13,0</t>
+          <t>9,96; 13,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,35; 13,41</t>
+          <t>10,36; 13,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,06; 20,16</t>
+          <t>17,58; 21,21</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>23534</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47704</t>
+          <t>54773</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6680; 21243</t>
+          <t>7179; 21743</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3950; 15475</t>
+          <t>3868; 14172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4791; 19042</t>
+          <t>5111; 18476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19659; 39580</t>
+          <t>22069; 41925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4527; 17006</t>
+          <t>5374; 18017</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2962; 13464</t>
+          <t>3000; 13520</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6161; 19647</t>
+          <t>6032; 20505</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13836; 26333</t>
+          <t>17695; 31948</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15526; 33145</t>
+          <t>15598; 35235</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8960; 23378</t>
+          <t>9379; 24619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13410; 32995</t>
+          <t>13435; 32850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37378; 59843</t>
+          <t>42580; 68050</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>33650</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3554; 14451</t>
+          <t>3408; 13590</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2830; 13649</t>
+          <t>3051; 13445</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4622; 17342</t>
+          <t>4778; 17677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10358; 24793</t>
+          <t>11166; 25641</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5806; 19182</t>
+          <t>5756; 18804</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4029; 15808</t>
+          <t>3957; 15175</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11158; 26470</t>
+          <t>11414; 27149</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10293; 22108</t>
+          <t>10888; 23891</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11800; 28610</t>
+          <t>11719; 27957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9771; 24897</t>
+          <t>9865; 25312</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18795; 39283</t>
+          <t>19883; 39075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23612; 41702</t>
+          <t>24695; 43025</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>27247</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8444; 22009</t>
+          <t>8573; 21896</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18965; 38820</t>
+          <t>18427; 39452</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4009; 16141</t>
+          <t>3473; 16939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7273; 18040</t>
+          <t>9107; 23059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2901; 13748</t>
+          <t>2685; 12773</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4180; 15717</t>
+          <t>3998; 15216</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2871; 12515</t>
+          <t>2086; 12140</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6668; 16074</t>
+          <t>7708; 17948</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13624; 30704</t>
+          <t>13461; 30769</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25483; 49485</t>
+          <t>23728; 47672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8616; 25053</t>
+          <t>8540; 24700</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16589; 32192</t>
+          <t>19108; 37347</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>35128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38320</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71017</t>
+          <t>79327</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21178; 40313</t>
+          <t>20342; 41857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24332; 48346</t>
+          <t>25135; 49824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26147; 49932</t>
+          <t>26723; 52234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23265; 44141</t>
+          <t>25448; 47733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13319; 31827</t>
+          <t>13460; 31420</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21686; 43730</t>
+          <t>20782; 41883</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20317; 41304</t>
+          <t>19512; 40909</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29589; 48493</t>
+          <t>34506; 54763</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38446; 64188</t>
+          <t>38929; 65689</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52047; 82512</t>
+          <t>52303; 84547</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51622; 83195</t>
+          <t>49793; 83193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58625; 86275</t>
+          <t>65112; 95651</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50822</t>
+          <t>56362</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3832; 13618</t>
+          <t>4319; 14820</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5483; 19038</t>
+          <t>5476; 18408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11995; 28745</t>
+          <t>12738; 29007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9550; 23429</t>
+          <t>10212; 24649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13458; 31140</t>
+          <t>12444; 29989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13646; 31319</t>
+          <t>13503; 31483</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22908; 45347</t>
+          <t>23639; 46561</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15284; 53019</t>
+          <t>31377; 49355</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20223; 39860</t>
+          <t>19018; 40673</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21835; 44039</t>
+          <t>22047; 43634</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40412; 67511</t>
+          <t>40149; 67217</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26542; 68559</t>
+          <t>46002; 69464</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35038</t>
+          <t>38331</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6060</t>
+          <t>0; 6206</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1932; 11689</t>
+          <t>1007; 11300</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1022; 8439</t>
+          <t>1018; 8361</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>429; 8657</t>
+          <t>411; 8181</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23207; 44228</t>
+          <t>23235; 46068</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30193; 54561</t>
+          <t>29290; 54780</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28831; 54069</t>
+          <t>29539; 54940</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23645; 43508</t>
+          <t>26226; 46223</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24860; 48568</t>
+          <t>25270; 47711</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34641; 60233</t>
+          <t>34334; 60460</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32050; 58322</t>
+          <t>32231; 59029</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25471; 46679</t>
+          <t>28317; 50274</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108110</t>
+          <t>117878</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>151519</t>
+          <t>171812</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>259629</t>
+          <t>289690</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>58925; 91922</t>
+          <t>57713; 92728</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>76505; 115353</t>
+          <t>75903; 113463</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69880; 108106</t>
+          <t>70285; 107819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90730; 126341</t>
+          <t>99578; 138552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>83660; 124655</t>
+          <t>84711; 124464</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96242; 140267</t>
+          <t>98077; 138469</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>116671; 163042</t>
+          <t>115529; 162750</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>106045; 173090</t>
+          <t>153397; 193019</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154951; 204881</t>
+          <t>154062; 203707</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185595; 240514</t>
+          <t>184243; 241257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>198714; 257442</t>
+          <t>198932; 254872</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>215089; 287907</t>
+          <t>261922; 316094</t>
         </is>
       </c>
     </row>
